--- a/sheets/대금율보/검수/소쇄원(瀟灑園).xlsx
+++ b/sheets/대금율보/검수/소쇄원(瀟灑園).xlsx
@@ -4015,7 +4015,7 @@
       <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南ʒ
-仲○
+仲
 –</t>
         </is>
       </c>
@@ -4135,7 +4135,7 @@
       <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太姑
-○仲ㅅ
+仲ㅅ
 –</t>
         </is>
       </c>
@@ -4143,7 +4143,7 @@
       <c r="R5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㒇太
-仲○
+仲
 –</t>
         </is>
       </c>
@@ -4171,7 +4171,7 @@
         <is>
           <t xml:space="preserve">–
 太
-仲○</t>
+仲</t>
         </is>
       </c>
       <c r="G6" s="22"/>
@@ -4214,13 +4214,13 @@
         <is>
           <t xml:space="preserve">–汰
 無南)
-仲○</t>
+仲</t>
         </is>
       </c>
       <c r="E7" s="22"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲○
+          <t xml:space="preserve">仲
 –
 姑太</t>
         </is>
@@ -4237,7 +4237,7 @@
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰∼∨
-仲○
+仲
 –</t>
         </is>
       </c>
@@ -4261,7 +4261,7 @@
       <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑ヲ
-仲○
+仲
 –</t>
         </is>
       </c>
@@ -4269,7 +4269,7 @@
       <c r="R7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㒇
-太仲○
+太仲
 –</t>
         </is>
       </c>
@@ -4318,7 +4318,7 @@
       <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑太
-仲○
+仲
 –</t>
         </is>
       </c>
@@ -4371,7 +4371,7 @@
       <c r="R9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌太
-仲○
+仲
 –</t>
         </is>
       </c>
@@ -4401,7 +4401,7 @@
         <is>
           <t xml:space="preserve">太∼姑
 –
-太仲○</t>
+太仲</t>
         </is>
       </c>
       <c r="I10" s="22"/>
@@ -4449,7 +4449,7 @@
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南ʒ
-仲○
+仲
 –</t>
         </is>
       </c>
@@ -4472,7 +4472,7 @@
       <c r="O11" s="22"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲○
+          <t xml:space="preserve">仲
 太)
 –△</t>
         </is>
@@ -4494,7 +4494,7 @@
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南ʒ
-仲○
+仲
 –</t>
         </is>
       </c>
@@ -4549,7 +4549,7 @@
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">ㅣ姑太∼
-–仲○
+–仲
 太)</t>
         </is>
       </c>
@@ -4573,7 +4573,7 @@
       <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-仲○
+仲
 –</t>
         </is>
       </c>
@@ -4597,7 +4597,7 @@
       <c r="C14" s="22"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑仲○
+          <t xml:space="preserve">姑仲
 –
 –</t>
         </is>
@@ -4621,7 +4621,7 @@
         <is>
           <t xml:space="preserve">–
 –姑
-仲○</t>
+仲</t>
         </is>
       </c>
       <c r="K14" s="22"/>
@@ -4650,7 +4650,7 @@
       <c r="C15" s="22"/>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑仲○
+          <t xml:space="preserve">姑仲
 –
 –</t>
         </is>
@@ -4756,14 +4756,14 @@
       <c r="C17" s="22"/>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲○ㅅ</t>
+          <t xml:space="preserve">仲ㅅ</t>
         </is>
       </c>
       <c r="E17" s="22"/>
       <c r="F17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-太仲○
+太仲
 –</t>
         </is>
       </c>
@@ -4789,7 +4789,7 @@
       <c r="P17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南ʒ
-仲○
+仲
 –</t>
         </is>
       </c>

--- a/sheets/대금율보/검수/소쇄원(瀟灑園).xlsx
+++ b/sheets/대금율보/검수/소쇄원(瀟灑園).xlsx
@@ -3936,30 +3936,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="18.03" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="18.03" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="18.03" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="18.03" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="18.03" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="18.03" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="18.03" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="18.03" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="18.03" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="102.56" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="114.74" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="S3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="114.74" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="22"/>
@@ -4094,7 +4094,7 @@
       <c r="R4" s="21"/>
       <c r="S4" s="22"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="114.74" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="S5" s="22"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="114.74" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
       <c r="R6" s="21"/>
       <c r="S6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="114.74" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="S7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="114.74" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
       <c r="R8" s="21"/>
       <c r="S8" s="22"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="114.74" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="S9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="114.74" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="22"/>
@@ -4426,7 +4426,7 @@
       <c r="R10" s="21"/>
       <c r="S10" s="22"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="114.74" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="S11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="114.74" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -4532,7 +4532,7 @@
       <c r="R12" s="21"/>
       <c r="S12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="114.74" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="22"/>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="S13" s="22"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="114.74" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="22"/>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="S14" s="22"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="114.74" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="S15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="114.74" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="22"/>
@@ -4750,7 +4750,7 @@
       <c r="R16" s="21"/>
       <c r="S16" s="22"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="114.74" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S17" s="22"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="114.74" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="22"/>
@@ -4864,6 +4864,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="67"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="39"/>
 </worksheet>
 </file>